--- a/WEN.xlsx
+++ b/WEN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16108B86-99E3-4A81-92B1-A57DC77B9A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5ECF251-6223-46FC-AE27-F98133FBFDB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="450" yWindow="2300" windowWidth="19890" windowHeight="16700" xr2:uid="{EF1C5987-CB25-4913-BCB5-878BA8991ACA}"/>
+    <workbookView xWindow="20160" yWindow="2100" windowWidth="14740" windowHeight="16580" xr2:uid="{EF1C5987-CB25-4913-BCB5-878BA8991ACA}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
   <si>
     <t>Price</t>
   </si>
@@ -166,6 +166,18 @@
   </si>
   <si>
     <t>SSS</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
   </si>
 </sst>
 </file>
@@ -269,8 +281,8 @@
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>33421</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>40105</xdr:rowOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>148897</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -285,8 +297,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4902868" y="20053"/>
-          <a:ext cx="0" cy="5156868"/>
+          <a:off x="4907593" y="20053"/>
+          <a:ext cx="0" cy="5970844"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -642,18 +654,18 @@
         <v>0</v>
       </c>
       <c r="N2" s="1">
-        <v>12</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="13:15" x14ac:dyDescent="0.25">
       <c r="M3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="2">
-        <v>192</v>
+      <c r="N3" s="3">
+        <v>190.48063999999999</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="13:15" x14ac:dyDescent="0.25">
@@ -662,7 +674,7 @@
       </c>
       <c r="N4" s="3">
         <f>+N2*N3</f>
-        <v>2304</v>
+        <v>1504.7970560000001</v>
       </c>
     </row>
     <row r="5" spans="13:15" x14ac:dyDescent="0.25">
@@ -670,11 +682,11 @@
         <v>3</v>
       </c>
       <c r="N5" s="3">
-        <f>335.259+26.77+34.644</f>
-        <v>396.673</v>
+        <f>298.74+39.295+24.499</f>
+        <v>362.53400000000005</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="13:15" x14ac:dyDescent="0.25">
@@ -682,11 +694,11 @@
         <v>4</v>
       </c>
       <c r="N6" s="3">
-        <f>78.334+2656.519</f>
-        <v>2734.8529999999996</v>
+        <f>2724.896+29.75</f>
+        <v>2754.6460000000002</v>
       </c>
       <c r="O6" s="4" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="13:15" x14ac:dyDescent="0.25">
@@ -695,7 +707,7 @@
       </c>
       <c r="N7" s="3">
         <f>+N4-N5+N6</f>
-        <v>4642.1799999999994</v>
+        <v>3896.9090560000004</v>
       </c>
     </row>
   </sheetData>
@@ -705,21 +717,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D671F29-85BA-4E8E-8E27-4E45D075D969}">
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:T41"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.6328125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" style="2" customWidth="1"/>
-    <col min="3" max="10" width="8.7265625" style="4"/>
-    <col min="11" max="16384" width="8.7265625" style="2"/>
+    <col min="3" max="14" width="8.7265625" style="4"/>
+    <col min="15" max="16384" width="8.7265625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
@@ -744,23 +756,35 @@
       <c r="J2" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="2">
+      <c r="K2" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="P2" s="2">
         <v>2021</v>
       </c>
-      <c r="M2" s="2">
+      <c r="Q2" s="2">
         <v>2021</v>
       </c>
-      <c r="N2" s="2">
+      <c r="R2" s="2">
         <v>2022</v>
       </c>
-      <c r="O2" s="2">
+      <c r="S2" s="2">
         <v>2023</v>
       </c>
-      <c r="P2" s="2">
+      <c r="T2" s="2">
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>37</v>
       </c>
@@ -774,17 +798,21 @@
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-      <c r="N3" s="3">
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="R3" s="3">
         <v>7095</v>
       </c>
-      <c r="O3" s="3">
+      <c r="S3" s="3">
         <v>7240</v>
       </c>
-      <c r="P3" s="3">
+      <c r="T3" s="3">
         <v>7240</v>
       </c>
     </row>
-    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>38</v>
       </c>
@@ -798,9 +826,13 @@
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
-      <c r="O4" s="9"/>
-    </row>
-    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="S4" s="9"/>
+    </row>
+    <row r="5" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>39</v>
       </c>
@@ -814,8 +846,12 @@
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
         <v>40</v>
       </c>
@@ -829,8 +865,12 @@
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
       <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
         <v>41</v>
       </c>
@@ -842,20 +882,24 @@
       <c r="H7" s="10"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
-      <c r="N7" s="3">
-        <f>+N11*1000000/N3</f>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="R7" s="3">
+        <f>+R11*1000000/R3</f>
         <v>78675.123326286121</v>
       </c>
-      <c r="O7" s="3">
-        <f>+O11*1000000/O3</f>
+      <c r="S7" s="3">
+        <f>+S11*1000000/S3</f>
         <v>81809.392265193368</v>
       </c>
-      <c r="P7" s="3">
-        <f>+P11*1000000/P3</f>
+      <c r="T7" s="3">
+        <f>+T11*1000000/T3</f>
         <v>86464.088397790052</v>
       </c>
     </row>
-    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
@@ -867,19 +911,23 @@
       <c r="H8" s="10"/>
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="11"/>
-      <c r="N8" s="11">
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11">
         <v>3.9E-2</v>
       </c>
-      <c r="O8" s="11">
+      <c r="S8" s="11">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="P8" s="11">
+      <c r="T8" s="11">
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="6"/>
@@ -888,8 +936,12 @@
       <c r="H9" s="10"/>
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K9" s="6"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B10" s="3" t="s">
         <v>16</v>
       </c>
@@ -905,23 +957,29 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
-      <c r="L10" s="3">
+      <c r="K10" s="6">
+        <v>225.49700000000001</v>
+      </c>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+      <c r="P10" s="3">
         <v>722.8</v>
       </c>
-      <c r="M10" s="3">
+      <c r="Q10" s="3">
         <v>734.1</v>
       </c>
-      <c r="N10" s="3">
+      <c r="R10" s="3">
         <v>896.6</v>
       </c>
-      <c r="O10" s="3">
+      <c r="S10" s="3">
         <v>930.1</v>
       </c>
-      <c r="P10" s="3">
+      <c r="T10" s="3">
         <v>925.9</v>
       </c>
     </row>
-    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
@@ -937,23 +995,29 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
-      <c r="L11" s="3">
+      <c r="K11" s="6">
+        <v>147.89500000000001</v>
+      </c>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="P11" s="3">
         <v>444.7</v>
       </c>
-      <c r="M11" s="3">
+      <c r="Q11" s="3">
         <v>536.70000000000005</v>
       </c>
-      <c r="N11" s="3">
+      <c r="R11" s="3">
         <v>558.20000000000005</v>
       </c>
-      <c r="O11" s="3">
+      <c r="S11" s="3">
         <v>592.29999999999995</v>
       </c>
-      <c r="P11" s="3">
+      <c r="T11" s="3">
         <v>626</v>
       </c>
     </row>
-    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B12" s="3" t="s">
         <v>18</v>
       </c>
@@ -969,23 +1033,29 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
-      <c r="L12" s="3">
+      <c r="K12" s="6">
+        <v>58.904000000000003</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="P12" s="3">
         <v>232.6</v>
       </c>
-      <c r="M12" s="3">
+      <c r="Q12" s="3">
         <v>236.7</v>
       </c>
-      <c r="N12" s="3">
+      <c r="R12" s="3">
         <v>234.5</v>
       </c>
-      <c r="O12" s="3">
+      <c r="S12" s="3">
         <v>230.2</v>
       </c>
-      <c r="P12" s="3">
+      <c r="T12" s="3">
         <v>236.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B13" s="3" t="s">
         <v>19</v>
       </c>
@@ -1001,23 +1071,29 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
-      <c r="L13" s="3">
+      <c r="K13" s="6">
+        <v>108.34099999999999</v>
+      </c>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="P13" s="3">
         <v>333.7</v>
       </c>
-      <c r="M13" s="3">
+      <c r="Q13" s="3">
         <v>389.5</v>
       </c>
-      <c r="N13" s="3">
+      <c r="R13" s="3">
         <v>406.2</v>
       </c>
-      <c r="O13" s="3">
+      <c r="S13" s="3">
         <v>429</v>
       </c>
-      <c r="P13" s="3">
+      <c r="T13" s="3">
         <v>458.1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" s="5" customFormat="1" ht="13" x14ac:dyDescent="0.3">
       <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
@@ -1041,31 +1117,47 @@
         <f>SUM(G10:G13)</f>
         <v>523.47199999999998</v>
       </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="L14" s="5">
-        <f t="shared" ref="L14" si="1">SUM(L10:L13)</f>
+      <c r="H14" s="7">
+        <f t="shared" ref="H14:K14" si="1">SUM(H10:H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K14" s="7">
+        <f t="shared" si="1"/>
+        <v>540.63700000000006</v>
+      </c>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="P14" s="5">
+        <f t="shared" ref="P14" si="2">SUM(P10:P13)</f>
         <v>1733.8</v>
       </c>
-      <c r="M14" s="5">
-        <f t="shared" ref="M14" si="2">SUM(M10:M13)</f>
+      <c r="Q14" s="5">
+        <f t="shared" ref="Q14" si="3">SUM(Q10:Q13)</f>
         <v>1897.0000000000002</v>
       </c>
-      <c r="N14" s="5">
-        <f t="shared" ref="N14:O14" si="3">SUM(N10:N13)</f>
+      <c r="R14" s="5">
+        <f t="shared" ref="R14:S14" si="4">SUM(R10:R13)</f>
         <v>2095.5</v>
       </c>
-      <c r="O14" s="5">
-        <f t="shared" si="3"/>
+      <c r="S14" s="5">
+        <f t="shared" si="4"/>
         <v>2181.6000000000004</v>
       </c>
-      <c r="P14" s="5">
-        <f>SUM(P10:P13)</f>
+      <c r="T14" s="5">
+        <f>SUM(T10:T13)</f>
         <v>2246.5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B15" s="3" t="s">
         <v>20</v>
       </c>
@@ -1081,71 +1173,96 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
       <c r="J15" s="6"/>
-      <c r="L15" s="3">
+      <c r="K15" s="6">
+        <v>201.04900000000001</v>
+      </c>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="P15" s="3">
         <v>614.9</v>
       </c>
-      <c r="M15" s="3">
+      <c r="Q15" s="3">
         <v>611.70000000000005</v>
       </c>
-      <c r="N15" s="3">
+      <c r="R15" s="3">
         <v>773.2</v>
       </c>
-      <c r="O15" s="3">
+      <c r="S15" s="3">
         <v>794.5</v>
       </c>
-      <c r="P15" s="3">
+      <c r="T15" s="3">
         <v>783.2</v>
       </c>
     </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
         <v>21</v>
       </c>
       <c r="C16" s="6">
-        <f t="shared" ref="C16:F16" si="4">+C14-C15</f>
+        <f t="shared" ref="C16:F16" si="5">+C14-C15</f>
         <v>342.63999999999993</v>
       </c>
       <c r="D16" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E16" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="F16" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G16" s="6">
         <f>+G14-G15</f>
         <v>335.303</v>
       </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
-      <c r="L16" s="3">
-        <f t="shared" ref="L16" si="5">+L14-L15</f>
+      <c r="H16" s="6">
+        <f t="shared" ref="H16:L16" si="6">+H14-H15</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="K16" s="6">
+        <f t="shared" si="6"/>
+        <v>339.58800000000008</v>
+      </c>
+      <c r="L16" s="6">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="P16" s="3">
+        <f t="shared" ref="P16" si="7">+P14-P15</f>
         <v>1118.9000000000001</v>
       </c>
-      <c r="M16" s="3">
-        <f t="shared" ref="M16" si="6">+M14-M15</f>
+      <c r="Q16" s="3">
+        <f t="shared" ref="Q16" si="8">+Q14-Q15</f>
         <v>1285.3000000000002</v>
       </c>
-      <c r="N16" s="3">
-        <f t="shared" ref="N16:O16" si="7">+N14-N15</f>
+      <c r="R16" s="3">
+        <f t="shared" ref="R16:S16" si="9">+R14-R15</f>
         <v>1322.3</v>
       </c>
-      <c r="O16" s="3">
-        <f t="shared" si="7"/>
+      <c r="S16" s="3">
+        <f t="shared" si="9"/>
         <v>1387.1000000000004</v>
       </c>
-      <c r="P16" s="3">
-        <f>+P14-P15</f>
+      <c r="T16" s="3">
+        <f>+T14-T15</f>
         <v>1463.3</v>
       </c>
     </row>
-    <row r="17" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B17" s="3" t="s">
         <v>17</v>
       </c>
@@ -1163,28 +1280,35 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
-      <c r="L17" s="3">
+      <c r="K17" s="6">
+        <f>21.991+30.176</f>
+        <v>52.167000000000002</v>
+      </c>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="P17" s="3">
         <f>26.5+125.6</f>
         <v>152.1</v>
       </c>
-      <c r="M17" s="3">
+      <c r="Q17" s="3">
         <f>42.9+132.4</f>
         <v>175.3</v>
       </c>
-      <c r="N17" s="3">
+      <c r="R17" s="3">
         <f>46.7+124.1</f>
         <v>170.8</v>
       </c>
-      <c r="O17" s="3">
+      <c r="S17" s="3">
         <f>57.2+125.4</f>
         <v>182.60000000000002</v>
       </c>
-      <c r="P17" s="3">
+      <c r="T17" s="3">
         <f>67.7+127.4</f>
         <v>195.10000000000002</v>
       </c>
     </row>
-    <row r="18" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
@@ -1200,23 +1324,29 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
-      <c r="L18" s="3">
+      <c r="K18" s="6">
+        <v>108.61499999999999</v>
+      </c>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="P18" s="3">
         <v>345.4</v>
       </c>
-      <c r="M18" s="3">
+      <c r="Q18" s="3">
         <v>411.8</v>
       </c>
-      <c r="N18" s="3">
+      <c r="R18" s="3">
         <v>430.8</v>
       </c>
-      <c r="O18" s="3">
+      <c r="S18" s="3">
         <v>428</v>
       </c>
-      <c r="P18" s="3">
+      <c r="T18" s="3">
         <v>478.1</v>
       </c>
     </row>
-    <row r="19" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B19" s="3" t="s">
         <v>22</v>
       </c>
@@ -1232,119 +1362,157 @@
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
-      <c r="L19" s="3">
+      <c r="K19" s="6">
+        <v>72.843000000000004</v>
+      </c>
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="P19" s="3">
         <v>206.9</v>
       </c>
-      <c r="M19" s="3">
+      <c r="Q19" s="3">
         <v>243</v>
       </c>
-      <c r="N19" s="3">
+      <c r="R19" s="3">
         <v>255</v>
       </c>
-      <c r="O19" s="3">
+      <c r="S19" s="3">
         <v>250</v>
       </c>
-      <c r="P19" s="3">
+      <c r="T19" s="3">
         <v>255.2</v>
       </c>
     </row>
-    <row r="20" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B20" s="3" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="6">
-        <f t="shared" ref="C20:F20" si="8">SUM(C17:C19)</f>
+        <f t="shared" ref="C20:F20" si="10">SUM(C17:C19)</f>
         <v>217.65100000000001</v>
       </c>
       <c r="D20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="E20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="F20" s="6">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="G20" s="6">
         <f>SUM(G17:G19)</f>
         <v>217.029</v>
       </c>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
-      <c r="L20" s="3">
-        <f t="shared" ref="L20" si="9">SUM(L17:L19)</f>
+      <c r="H20" s="6">
+        <f t="shared" ref="H20:L20" si="11">SUM(H17:H19)</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="6">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="K20" s="6">
+        <f t="shared" si="11"/>
+        <v>233.625</v>
+      </c>
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="P20" s="3">
+        <f t="shared" ref="P20" si="12">SUM(P17:P19)</f>
         <v>704.4</v>
       </c>
-      <c r="M20" s="3">
-        <f t="shared" ref="M20" si="10">SUM(M17:M19)</f>
+      <c r="Q20" s="3">
+        <f t="shared" ref="Q20" si="13">SUM(Q17:Q19)</f>
         <v>830.1</v>
       </c>
-      <c r="N20" s="3">
-        <f t="shared" ref="N20:O20" si="11">SUM(N17:N19)</f>
+      <c r="R20" s="3">
+        <f t="shared" ref="R20:S20" si="14">SUM(R17:R19)</f>
         <v>856.6</v>
       </c>
-      <c r="O20" s="3">
-        <f t="shared" si="11"/>
+      <c r="S20" s="3">
+        <f t="shared" si="14"/>
         <v>860.6</v>
       </c>
-      <c r="P20" s="3">
-        <f>SUM(P17:P19)</f>
+      <c r="T20" s="3">
+        <f>SUM(T17:T19)</f>
         <v>928.40000000000009</v>
       </c>
     </row>
-    <row r="21" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B21" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="6">
-        <f t="shared" ref="C21:F21" si="12">C16-C20</f>
+        <f t="shared" ref="C21:F21" si="15">C16-C20</f>
         <v>124.98899999999992</v>
       </c>
       <c r="D21" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="E21" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="F21" s="6">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G21" s="6">
         <f>G16-G20</f>
         <v>118.274</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
-      <c r="L21" s="3">
-        <f t="shared" ref="L21" si="13">L16-L20</f>
+      <c r="H21" s="6">
+        <f t="shared" ref="H21:L21" si="16">H16-H20</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="6">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="K21" s="6">
+        <f t="shared" si="16"/>
+        <v>105.96300000000008</v>
+      </c>
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="P21" s="3">
+        <f t="shared" ref="P21" si="17">P16-P20</f>
         <v>414.50000000000011</v>
       </c>
-      <c r="M21" s="3">
-        <f t="shared" ref="M21" si="14">M16-M20</f>
+      <c r="Q21" s="3">
+        <f t="shared" ref="Q21" si="18">Q16-Q20</f>
         <v>455.20000000000016</v>
       </c>
-      <c r="N21" s="3">
-        <f t="shared" ref="N21:O21" si="15">N16-N20</f>
+      <c r="R21" s="3">
+        <f t="shared" ref="R21:S21" si="19">R16-R20</f>
         <v>465.69999999999993</v>
       </c>
-      <c r="O21" s="3">
-        <f t="shared" si="15"/>
+      <c r="S21" s="3">
+        <f t="shared" si="19"/>
         <v>526.50000000000034</v>
       </c>
-      <c r="P21" s="3">
-        <f>P16-P20</f>
+      <c r="T21" s="3">
+        <f>T16-T20</f>
         <v>534.89999999999986</v>
       </c>
     </row>
-    <row r="22" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B22" s="3" t="s">
         <v>25</v>
       </c>
@@ -1358,71 +1526,93 @@
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
-      <c r="L22" s="3">
+      <c r="K22" s="6">
+        <v>-34.106000000000002</v>
+      </c>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="P22" s="3">
         <v>-117.7</v>
       </c>
-      <c r="M22" s="3">
+      <c r="Q22" s="3">
         <v>-109.2</v>
       </c>
-      <c r="N22" s="3">
+      <c r="R22" s="3">
         <v>-122.3</v>
       </c>
-      <c r="O22" s="3">
+      <c r="S22" s="3">
         <v>-124.1</v>
       </c>
-      <c r="P22" s="3">
+      <c r="T22" s="3">
         <v>-123.9</v>
       </c>
     </row>
-    <row r="23" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C23" s="6">
-        <f t="shared" ref="C23:F23" si="16">+C21+C22</f>
+        <f t="shared" ref="C23:F23" si="20">+C21+C22</f>
         <v>124.98899999999992</v>
       </c>
       <c r="D23" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="E23" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F23" s="6">
-        <f t="shared" si="16"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="G23" s="6">
         <f>+G21+G22</f>
         <v>86.796999999999997</v>
       </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-      <c r="L23" s="3">
-        <f t="shared" ref="L23" si="17">+L21+L22</f>
+      <c r="H23" s="6">
+        <f t="shared" ref="H23:K23" si="21">+H21+H22</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="6">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="K23" s="6">
+        <f t="shared" si="21"/>
+        <v>71.857000000000085</v>
+      </c>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="P23" s="3">
+        <f t="shared" ref="P23" si="22">+P21+P22</f>
         <v>296.80000000000013</v>
       </c>
-      <c r="M23" s="3">
-        <f t="shared" ref="M23" si="18">+M21+M22</f>
+      <c r="Q23" s="3">
+        <f t="shared" ref="Q23" si="23">+Q21+Q22</f>
         <v>346.00000000000017</v>
       </c>
-      <c r="N23" s="3">
-        <f>+N21+N22</f>
+      <c r="R23" s="3">
+        <f>+R21+R22</f>
         <v>343.39999999999992</v>
       </c>
-      <c r="O23" s="3">
-        <f>+O21+O22</f>
+      <c r="S23" s="3">
+        <f>+S21+S22</f>
         <v>402.40000000000032</v>
       </c>
-      <c r="P23" s="3">
-        <f>+P21+P22</f>
+      <c r="T23" s="3">
+        <f>+T21+T22</f>
         <v>410.99999999999989</v>
       </c>
     </row>
-    <row r="24" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B24" s="3" t="s">
         <v>27</v>
       </c>
@@ -1438,88 +1628,110 @@
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
-      <c r="L24" s="3">
+      <c r="K24" s="6">
+        <v>11.452999999999999</v>
+      </c>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="P24" s="3">
         <v>35</v>
       </c>
-      <c r="M24" s="3">
+      <c r="Q24" s="3">
         <v>40.200000000000003</v>
       </c>
-      <c r="N24" s="3">
+      <c r="R24" s="3">
         <v>66.099999999999994</v>
       </c>
-      <c r="O24" s="3">
+      <c r="S24" s="3">
         <v>75</v>
       </c>
-      <c r="P24" s="3">
+      <c r="T24" s="3">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B25" s="3" t="s">
         <v>28</v>
       </c>
       <c r="C25" s="6">
-        <f t="shared" ref="C25:F25" si="19">+C23-C24</f>
+        <f t="shared" ref="C25:F25" si="24">+C23-C24</f>
         <v>109.52499999999992</v>
       </c>
       <c r="D25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="E25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F25" s="6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="G25" s="6">
         <f>+G23-G24</f>
         <v>71.111999999999995</v>
       </c>
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
-      <c r="L25" s="3">
-        <f t="shared" ref="L25" si="20">+L23-L24</f>
+      <c r="H25" s="6">
+        <f t="shared" ref="H25:K25" si="25">+H23-H24</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="J25" s="6">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="K25" s="6">
+        <f t="shared" si="25"/>
+        <v>60.404000000000082</v>
+      </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="P25" s="3">
+        <f t="shared" ref="P25" si="26">+P23-P24</f>
         <v>261.80000000000013</v>
       </c>
-      <c r="M25" s="3">
-        <f t="shared" ref="M25" si="21">+M23-M24</f>
+      <c r="Q25" s="3">
+        <f t="shared" ref="Q25" si="27">+Q23-Q24</f>
         <v>305.80000000000018</v>
       </c>
-      <c r="N25" s="3">
-        <f>+N23-N24</f>
+      <c r="R25" s="3">
+        <f>+R23-R24</f>
         <v>277.29999999999995</v>
       </c>
-      <c r="O25" s="3">
-        <f>+O23-O24</f>
+      <c r="S25" s="3">
+        <f>+S23-S24</f>
         <v>327.40000000000032</v>
       </c>
-      <c r="P25" s="3">
-        <f>+P23-P24</f>
+      <c r="T25" s="3">
+        <f>+T23-T24</f>
         <v>332.99999999999989</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B26" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="10">
-        <f t="shared" ref="C26:F26" si="22">+C25/C27</f>
+        <f t="shared" ref="C26:F26" si="28">+C25/C27</f>
         <v>0.52918041658010018</v>
       </c>
       <c r="D26" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E26" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F26" s="10" t="e">
-        <f t="shared" si="22"/>
+        <f t="shared" si="28"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G26" s="10">
@@ -1527,7 +1739,7 @@
         <v>0.35270835296626774</v>
       </c>
     </row>
-    <row r="27" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="3" t="s">
         <v>1</v>
       </c>
@@ -1543,8 +1755,12 @@
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
-    </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="K27" s="6"/>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="29" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B29" s="2" t="s">
         <v>29</v>
       </c>
@@ -1552,24 +1768,28 @@
         <f>+G14/C14-1</f>
         <v>-2.1095720828120501E-2</v>
       </c>
-      <c r="M29" s="9">
-        <f>+M14/L14-1</f>
+      <c r="K29" s="8">
+        <f>+K14/G14-1</f>
+        <v>3.2790674572852119E-2</v>
+      </c>
+      <c r="Q29" s="9">
+        <f>+Q14/P14-1</f>
         <v>9.4128503864344459E-2</v>
       </c>
-      <c r="N29" s="9">
-        <f t="shared" ref="N29:P29" si="23">+N14/M14-1</f>
+      <c r="R29" s="9">
+        <f t="shared" ref="R29:T29" si="29">+R14/Q14-1</f>
         <v>0.10463890353189242</v>
       </c>
-      <c r="O29" s="9">
-        <f t="shared" si="23"/>
+      <c r="S29" s="9">
+        <f t="shared" si="29"/>
         <v>4.1088045812455398E-2</v>
       </c>
-      <c r="P29" s="9">
-        <f t="shared" si="23"/>
+      <c r="T29" s="9">
+        <f t="shared" si="29"/>
         <v>2.9748808214154598E-2</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B30" s="9" t="s">
         <v>30</v>
       </c>
@@ -1578,23 +1798,27 @@
         <v>0.64074441845113539</v>
       </c>
       <c r="D30" s="8" t="e">
-        <f t="shared" ref="D30:G30" si="24">+D16/D14</f>
+        <f t="shared" ref="D30:G30" si="30">+D16/D14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="E30" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F30" s="8" t="e">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>#DIV/0!</v>
       </c>
       <c r="G30" s="8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="30"/>
         <v>0.64053664761439011</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="K30" s="8">
+        <f t="shared" ref="K30" si="31">+K16/K14</f>
+        <v>0.62812571096687808</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
         <v>31</v>
       </c>
@@ -1610,23 +1834,29 @@
       <c r="H33" s="6"/>
       <c r="I33" s="6"/>
       <c r="J33" s="6"/>
-      <c r="L33" s="3">
+      <c r="K33" s="6">
+        <v>59.389000000000003</v>
+      </c>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="P33" s="3">
         <v>284.36099999999999</v>
       </c>
-      <c r="M33" s="3">
+      <c r="Q33" s="3">
         <v>345.77199999999999</v>
       </c>
-      <c r="N33" s="3">
+      <c r="R33" s="3">
         <v>259.904</v>
       </c>
-      <c r="O33" s="3">
+      <c r="S33" s="3">
         <v>345.416</v>
       </c>
-      <c r="P33" s="3">
+      <c r="T33" s="3">
         <v>355.30700000000002</v>
       </c>
     </row>
-    <row r="34" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B34" s="3" t="s">
         <v>33</v>
       </c>
@@ -1642,23 +1872,29 @@
       <c r="H34" s="6"/>
       <c r="I34" s="6"/>
       <c r="J34" s="6"/>
-      <c r="L34" s="3">
+      <c r="K34" s="6">
+        <v>11.458</v>
+      </c>
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="P34" s="3">
         <v>68.968999999999994</v>
       </c>
-      <c r="M34" s="3">
+      <c r="Q34" s="3">
         <v>77.983999999999995</v>
       </c>
-      <c r="N34" s="3">
+      <c r="R34" s="3">
         <v>85.543999999999997</v>
       </c>
-      <c r="O34" s="3">
+      <c r="S34" s="3">
         <v>85.021000000000001</v>
       </c>
-      <c r="P34" s="3">
+      <c r="T34" s="3">
         <v>94.388000000000005</v>
       </c>
     </row>
-    <row r="35" spans="2:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B35" s="3" t="s">
         <v>32</v>
       </c>
@@ -1673,31 +1909,47 @@
         <f>+G33-G34</f>
         <v>67.736000000000004</v>
       </c>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="L35" s="3">
-        <f t="shared" ref="L35:M35" si="25">+L33-L34</f>
+      <c r="H35" s="6">
+        <f t="shared" ref="H35:K35" si="32">+H33-H34</f>
+        <v>0</v>
+      </c>
+      <c r="I35" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="J35" s="6">
+        <f t="shared" si="32"/>
+        <v>0</v>
+      </c>
+      <c r="K35" s="6">
+        <f t="shared" si="32"/>
+        <v>47.931000000000004</v>
+      </c>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="P35" s="3">
+        <f t="shared" ref="P35:Q35" si="33">+P33-P34</f>
         <v>215.392</v>
       </c>
-      <c r="M35" s="3">
-        <f t="shared" si="25"/>
+      <c r="Q35" s="3">
+        <f t="shared" si="33"/>
         <v>267.78800000000001</v>
       </c>
-      <c r="N35" s="3">
-        <f>+N33-N34</f>
+      <c r="R35" s="3">
+        <f>+R33-R34</f>
         <v>174.36</v>
       </c>
-      <c r="O35" s="3">
-        <f>+O33-O34</f>
+      <c r="S35" s="3">
+        <f>+S33-S34</f>
         <v>260.39499999999998</v>
       </c>
-      <c r="P35" s="3">
-        <f>+P33-P34</f>
+      <c r="T35" s="3">
+        <f>+T33-T34</f>
         <v>260.91899999999998</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B40" s="2" t="s">
         <v>35</v>
       </c>
@@ -1706,7 +1958,7 @@
         <v>0.14277709443761097</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:20" x14ac:dyDescent="0.25">
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
